--- a/data/trans_orig/IP31KM16_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP31KM16_2023-Estudios-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>8745</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>4551</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>14057</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>16,28%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>8,47%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>26,17%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>15877</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>9149</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>28350</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>29,57%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>17,04%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>52,79%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>9336</t>
+          <t>11021</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>6838</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15559</t>
+          <t>16474</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>24,01%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>26,67%</t>
+          <t>35,89%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>25212</t>
+          <t>19766</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>16787</t>
+          <t>13772</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>41306</t>
+          <t>27054</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>19,84%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>36,87%</t>
+          <t>27,16%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>44970</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>39658</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>49164</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>83,72%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>73,83%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>91,53%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>50</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>37822</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>25349</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>44550</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>70,43%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>47,21%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>82,96%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>49009</t>
+          <t>34884</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>42786</t>
+          <t>29431</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>53184</t>
+          <t>39067</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>84,0%</t>
+          <t>75,99%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>73,33%</t>
+          <t>64,11%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,15%</t>
+          <t>85,1%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>86831</t>
+          <t>79854</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>70737</t>
+          <t>72566</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>95256</t>
+          <t>85848</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>77,5%</t>
+          <t>80,16%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>63,13%</t>
+          <t>72,84%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>85,02%</t>
+          <t>86,18%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>53715</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>53715</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>53715</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>53699</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>53699</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>53699</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>58345</t>
+          <t>45905</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>58345</t>
+          <t>45905</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>58345</t>
+          <t>45905</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>112043</t>
+          <t>99620</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>112043</t>
+          <t>99620</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>112043</t>
+          <t>99620</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>58569</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>43232</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>84900</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>12,56%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>9,27%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>18,2%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>75</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>53514</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>41184</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>67088</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>11,84%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>9,11%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>14,85%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>62812</t>
+          <t>52604</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>47640</t>
+          <t>42171</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>103583</t>
+          <t>64289</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>116326</t>
+          <t>111173</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>95854</t>
+          <t>93037</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>150150</t>
+          <t>141978</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>15,93%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>560</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>407854</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>381523</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>423191</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>87,44%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>81,8%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>90,73%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>550</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>398318</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>384744</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>410648</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>88,16%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>85,15%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>90,89%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>560</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>442438</t>
+          <t>372062</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>401667</t>
+          <t>360377</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>457610</t>
+          <t>382495</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>87,57%</t>
+          <t>87,61%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>79,5%</t>
+          <t>84,86%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,57%</t>
+          <t>90,07%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>840756</t>
+          <t>779917</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>806932</t>
+          <t>749112</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>861228</t>
+          <t>798053</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>87,85%</t>
+          <t>87,52%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>84,31%</t>
+          <t>84,07%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>89,98%</t>
+          <t>89,56%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>630</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>466423</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>466423</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>466423</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>625</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>451832</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>451832</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>451832</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>630</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>505250</t>
+          <t>424666</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>505250</t>
+          <t>424666</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>505250</t>
+          <t>424666</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>957082</t>
+          <t>891090</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>957082</t>
+          <t>891090</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>957082</t>
+          <t>891090</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>20274</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>12781</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>29037</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>12,16%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>7,67%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>17,42%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>16827</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>10887</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>25643</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>11,51%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>7,45%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>17,54%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>21614</t>
+          <t>16996</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14041</t>
+          <t>11331</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>30754</t>
+          <t>24997</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>16,99%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>38440</t>
+          <t>37270</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>28914</t>
+          <t>27685</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>49370</t>
+          <t>48607</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>15,49%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>205</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>146412</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>137649</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>153905</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>87,84%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>82,58%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>92,33%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>199</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>129359</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>120543</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>135299</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>88,49%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>82,46%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>92,55%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>205</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>159525</t>
+          <t>130144</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>150385</t>
+          <t>122143</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>167098</t>
+          <t>135809</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>88,07%</t>
+          <t>88,45%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>83,02%</t>
+          <t>83,01%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,25%</t>
+          <t>92,3%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>288884</t>
+          <t>276555</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>277954</t>
+          <t>265218</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>298410</t>
+          <t>286140</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>88,26%</t>
+          <t>88,12%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>84,92%</t>
+          <t>84,51%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,17%</t>
+          <t>91,18%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>233</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>166686</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>166686</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>166686</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>222</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>146186</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>146186</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>146186</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>233</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>181139</t>
+          <t>147140</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>181139</t>
+          <t>147140</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>181139</t>
+          <t>147140</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>327324</t>
+          <t>313825</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>327324</t>
+          <t>313825</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>327324</t>
+          <t>313825</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>87588</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>70780</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>112471</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>12,75%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>10,31%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>16,38%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>115</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>86218</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>69781</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>108149</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>13,23%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>10,71%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>16,59%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>93761</t>
+          <t>80621</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>76109</t>
+          <t>66982</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>130845</t>
+          <t>95205</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,17 +1824,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>179979</t>
+          <t>168209</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>154224</t>
+          <t>145003</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>213331</t>
+          <t>195676</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>15,0%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>830</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>599236</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>574353</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>616044</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>87,25%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>83,62%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>89,69%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>799</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>565499</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>543568</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>581936</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>86,77%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>83,41%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>89,29%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>830</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>650972</t>
+          <t>537090</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>613888</t>
+          <t>522506</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>668624</t>
+          <t>550729</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>87,41%</t>
+          <t>86,95%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>82,43%</t>
+          <t>84,59%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,78%</t>
+          <t>89,16%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,17 +1937,17 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1216471</t>
+          <t>1136326</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1183119</t>
+          <t>1108859</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1242226</t>
+          <t>1159532</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>84,72%</t>
+          <t>85,0%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,96%</t>
+          <t>88,88%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>940</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>914</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>651717</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>651717</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>651717</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>940</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>617711</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>617711</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>617711</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1396450</t>
+          <t>1304535</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1396450</t>
+          <t>1304535</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1396450</t>
+          <t>1304535</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
